--- a/Results.xlsx
+++ b/Results.xlsx
@@ -600,6 +600,9 @@
       <c r="B3" s="2" t="n">
         <v>0.996</v>
       </c>
+      <c r="C3" t="n">
+        <v>0.972</v>
+      </c>
       <c r="D3" s="2" t="n">
         <v>0.996</v>
       </c>
@@ -631,14 +634,20 @@
           <t>causal_judgement</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>0.6578000000000001</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6257</v>
+      </c>
       <c r="D4" s="2" t="n">
         <v>0.6417</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.615</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6898</v>
+        <v>0.6952</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.6791</v>
@@ -662,14 +671,20 @@
           <t>date_understanding</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9</v>
+      </c>
       <c r="D5" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9</v>
+        <v>0.908</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.9399999999999999</v>
@@ -693,26 +708,32 @@
           <t>dyck_languages</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.74</v>
+      </c>
       <c r="D6" s="2" t="n">
         <v>0.756</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.416</v>
+        <v>0.696</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.828</v>
+        <v>0.956</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.836</v>
+        <v>0.856</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.472</v>
+        <v>0.556</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0.376</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.572</v>
+        <v>0.944</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.64</v>
@@ -724,14 +745,20 @@
           <t>formal_fallacies</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.996</v>
+      </c>
       <c r="D7" s="2" t="n">
         <v>0.996</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.968</v>
+        <v>0.984</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.912</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1</v>
@@ -752,6 +779,12 @@
           <t>geometric_shapes</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.792</v>
+      </c>
       <c r="D8" s="2" t="n">
         <v>0.768</v>
       </c>
@@ -759,7 +792,7 @@
         <v>0.8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.648</v>
+        <v>0.804</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.8</v>
@@ -783,6 +816,12 @@
           <t>logical_deduction_five_objects</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.996</v>
+      </c>
       <c r="D9" s="2" t="n">
         <v>1</v>
       </c>
@@ -796,7 +835,7 @@
         <v>0.984</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.152</v>
+        <v>0.156</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>0.876</v>
@@ -814,11 +853,17 @@
           <t>logical_deduction_seven_objects</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.984</v>
+      </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -827,7 +872,7 @@
         <v>0.992</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0.8159999999999999</v>
@@ -845,6 +890,12 @@
           <t>logical_deduction_three_objects</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.992</v>
+      </c>
       <c r="D11" s="2" t="n">
         <v>1</v>
       </c>
@@ -876,6 +927,12 @@
           <t>multistep_arithmetic_two</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.992</v>
+      </c>
       <c r="D12" s="2" t="n">
         <v>0.996</v>
       </c>
@@ -904,6 +961,12 @@
           <t>navigate</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.992</v>
+      </c>
       <c r="D13" s="2" t="n">
         <v>1</v>
       </c>
@@ -932,11 +995,17 @@
           <t>object_counting</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.98</v>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>0.88</v>
+        <v>0.972</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.992</v>
+        <v>0.996</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
@@ -945,7 +1014,7 @@
         <v>0.996</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.92</v>
+        <v>0.944</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0.924</v>
@@ -960,11 +1029,17 @@
           <t>penguins_in_a_table</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9932</v>
+      </c>
       <c r="D15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9315</v>
+        <v>0.9932</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
@@ -988,11 +1063,17 @@
           <t>reasoning_about_colored_objects</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.984</v>
+      </c>
       <c r="D16" s="2" t="n">
         <v>0.988</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.952</v>
+        <v>0.992</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0.988</v>
@@ -1019,11 +1100,17 @@
           <t>temporal_sequences</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.996</v>
+      </c>
       <c r="D17" s="2" t="n">
         <v>0.992</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.992</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0.984</v>
@@ -1050,11 +1137,17 @@
           <t>tracking_shuffled_objects_five_objects</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.976</v>
+      </c>
       <c r="D18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.988</v>
+        <v>0.996</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
@@ -1078,11 +1171,17 @@
           <t>tracking_shuffled_objects_seven_objects</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.984</v>
+      </c>
       <c r="D19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.868</v>
+        <v>0.964</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
@@ -1106,11 +1205,17 @@
           <t>tracking_shuffled_objects_three_objects</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.996</v>
+      </c>
       <c r="D20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.908</v>
+        <v>0.996</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
@@ -1134,23 +1239,29 @@
           <t>web_of_lies</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.852</v>
+      </c>
       <c r="D21" s="2" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>0.944</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0.916</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0.716</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0.888</v>
@@ -1162,11 +1273,17 @@
           <t>word_sorting</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.956</v>
+      </c>
       <c r="D22" s="2" t="n">
         <v>0.908</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.86</v>
+        <v>0.784</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
@@ -1190,25 +1307,29 @@
           <t>Overall Score (macro-avg of 20 tasks)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
+      <c r="B23" s="3" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0.9349</v>
+      </c>
       <c r="D23" s="4" t="n">
-        <v>0.9403</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.9015</v>
+        <v>0.9339</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9493</v>
+        <v>0.9684</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.9606</v>
+        <v>0.9616</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3387</v>
+        <v>0.3455</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.8337</v>
+        <v>0.8451</v>
       </c>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="4" t="n">
@@ -2426,7 +2547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2438,10 +2559,11 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Results.xlsx — Every model that has appeared in an experiment. Rebuilt 2026-08-29 from the result files on disk.</t>
-        </is>
-      </c>
-    </row>
+          <t>Results.xlsx — Every model that has appeared in an experiment. Rebuilt 2026-08-29 from the result files on disk; bbh refreshed 2026-09-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2521,12 +2643,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Tasks_benchmarks/bbh/BBH_*/results/*_bbh_overall.csv</t>
+          <t>Tasks_benchmarks/bbh/BBH_*/results/&lt;task&gt;/&lt;model&gt;_overall.csv</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Refreshed 2026-08-29 from the uniform rescore, scorer tag lenient_v2: every model scored by the same six-branch matcher out of bbh_eval_core.py. The sheet is now reproducible from one source, and the old strict-vs-lenient caveat no longer applies here.</t>
+          <t>Refreshed 2026-09-07 from the per-task CSVs, scorer tag lenient_v5 (uniform across all 10 slots): every model scored by the same matcher out of bbh_eval_core.py. Read the per-task files, NOT the slot-level BBH_*/results/*_bbh_overall.csv — the DeepInfra repair of 2026-08-30 re-ran only the affected tasks and overwrote Gemma’s roll-up with 5 tasks and Qwen’s with 13, understating them by 0.089 and 0.019.</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2665,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>1 of 20 tasks — run in progress</t>
+          <t>20 of 20 tasks — complete</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>The selected Gemini has started on bbh. Only the tasks it has finished carry a value; Overall Score stays blank until all 20 are in.</t>
+          <t>BBH_Gemini_Flash3.5lite_OpenRouter, 4,833 rows, macro 0.9375, no_marker 0, empty 0. Run 2026-08-29 on the settled OpenRouter route (google/gemini-3.5-flash-lite). This column no longer belongs to the superseded gemini-2.5-flash, which keeps its own column here.</t>
         </is>
       </c>
     </row>
@@ -2565,34 +2687,34 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>blank — not yet run</t>
+          <t>20 of 20 tasks — complete</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>BBH_GPT_5.6_Luna has a runner but no results.</t>
+          <t>BBH_GPT_5.6_Luna, 4,833 rows, macro 0.9349, no_marker 0, empty 0. Run 2026-08-29 at reasoning_effort="low", the settled config. Its output cap is chosen rather than measured, and no task came back truncated at it.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Big Bench Hard</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Overall Score</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>macro-average over the 20 tasks</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Written only for a column with all 20, so the row stays comparable. Kimi has 10 tasks and a 10-task macro of 0.8938, which is deliberately not put in a row labelled 20.</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Qwen = Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20 of 20 tasks — complete, 17 rows unusable</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BBH_Qwen, 4,833 rows, macro 0.9339. The DeepInfra repair of 2026-08-30 took 256 unusable rows down to 17 — 16 no_marker and 1 empty, all in dyck_languages, which is scored 0.696 with them counted as wrong. No other slot among the six has any.</t>
         </is>
       </c>
     </row>
@@ -2604,17 +2726,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Gemini-2.5-Flash</t>
+          <t>Overall Score</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>BBH_Gemini_Flash2.5, macro 0.3387</t>
+          <t>macro-average over the 20 tasks</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>A BROKEN RUN, kept as a record. 3,002 of its 4,833 responses never emitted "Final Answer:", so no scorer can rescue them — the lenient matcher has nothing to match. This replaces the 0.9122 the workbook carried until 2026-08-29, whose source run is not on disk. The model is superseded, so it will not be redone.</t>
+          <t>Written only for a column with all 20, so the row stays comparable. Kimi has 10 tasks and a 10-task macro of 0.9310, which is deliberately not put in a row labelled 20.</t>
         </is>
       </c>
     </row>
@@ -2626,39 +2748,39 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>GPT-4o-mini · Kimi · Llama</t>
+          <t>Gemini-2.5-Flash</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>their BBH_* overall CSVs</t>
+          <t>BBH_Gemini_Flash2.5, macro 0.3455</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>gpt-4o-mini 0.8337 (superseded), llama 0.9109, kimi 10 tasks. Kimi and Llama were never among the six; the rescore gave them real numbers where this workbook previously had empty columns.</t>
+          <t>A BROKEN RUN, kept as a record. 3,002 of its 4,833 responses never emitted "Final Answer:", so no scorer can rescue them — the lenient matcher has nothing to match. This replaces the 0.9122 the workbook carried until 2026-08-29, whose source run is not on disk. The model is superseded and the slot is now gemini-3.5-flash-lite, so it will not be redone.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>GPT-4o-mini · Kimi · Llama</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>mmlu &lt;model&gt;_overall_results.csv</t>
+          <t>their per-task overall CSVs</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Matches the previous workbook.</t>
+          <t>gpt-4o-mini 0.8451 (superseded), llama 0.9109, kimi 10 of 20 tasks. Kimi and Llama were never among the six; the rescore gave them real numbers where this workbook previously had empty columns.</t>
         </is>
       </c>
     </row>
@@ -2670,17 +2792,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>XAI · Deepseek</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>mmlu/gemma/gemma_overall_results.csv</t>
+          <t>mmlu &lt;model&gt;_overall_results.csv</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>8 of 13 subjects; the other five were never written.</t>
+          <t>Matches the previous workbook.</t>
         </is>
       </c>
     </row>
@@ -2692,61 +2814,61 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>mmlu/gemma/gemma_overall_results.csv</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>qwen_overall_results.csv exists but is empty.</t>
+          <t>8 of 13 subjects; the other five were never written.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>MMLU · DocVQA</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>scoring</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>still per-runner</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Only bbh has been moved onto one shared lenient matcher. Until MMLU and DocVQA follow, their columns are not guaranteed to be scored the same way as each other.</t>
+          <t>qwen_overall_results.csv exists but is empty.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>DocVQA</t>
+          <t>MMLU · DocVQA</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Qwen · Gemma</t>
+          <t>scoring</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
+          <t>still per-runner</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
+          <t>Only bbh has been moved onto one shared lenient matcher. Until MMLU and DocVQA follow, their columns are not guaranteed to be scored the same way as each other.</t>
         </is>
       </c>
     </row>
@@ -2758,39 +2880,39 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>Qwen · Gemma</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>No DocVQA run exists.</t>
+          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Emo</t>
+          <t>DocVQA</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>XAI · Deepseek</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
+          <t>No DocVQA run exists.</t>
         </is>
       </c>
     </row>
@@ -2802,17 +2924,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
+          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
+          <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
         </is>
       </c>
     </row>
@@ -2824,37 +2946,59 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>XAI · Qwen · Gemma · Deepseek</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>EmoBench/emobench_results.csv</t>
+          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Unchanged.</t>
+          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
+          <t>Emo</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>XAI · Qwen · Gemma · Deepseek</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>EmoBench/emobench_results.csv</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>Awareness</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>every column</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>No model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
         </is>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1347,7 +1347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1398,6 +1398,16 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Gemini-2.5-Flash</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>GPT-4o-mini</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Llama</t>
         </is>
       </c>
@@ -1410,35 +1420,45 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
+          <t>gemini-3.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>gpt-5.6-luna</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>grok-3-mini</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>google/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>deepseek-reasoner</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
           <t>gemini-2.5-flash</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>grok-3-mini</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Qwen/Qwen3.5-9B</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>google/gemma-4-31B-it</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>meta-llama/Llama-4-Maverick-17B-128E-Instruct-FP8</t>
         </is>
@@ -1451,20 +1471,29 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.82</v>
       </c>
+      <c r="E3" t="n">
+        <v>0.83</v>
+      </c>
       <c r="F3" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.83</v>
       </c>
+      <c r="H3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1473,19 +1502,28 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.588</v>
+        <v>0.8333</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8509</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.842</v>
+        <v>0.8421</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.904</v>
+        <v>0.9035</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5877</v>
       </c>
     </row>
     <row r="5">
@@ -1495,19 +1533,28 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.929</v>
+        <v>0.9841</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.958</v>
+        <v>0.9841</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.979</v>
+        <v>0.9788</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9788</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.984</v>
+        <v>0.9841</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.981</v>
+        <v>0.9815</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9577</v>
       </c>
     </row>
     <row r="6">
@@ -1517,16 +1564,28 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9365</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.643</v>
+        <v>0.9683</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.976</v>
+        <v>0.9762</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9365</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9762</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.976</v>
+        <v>0.9762</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9603</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6429</v>
       </c>
     </row>
     <row r="7">
@@ -1536,19 +1595,28 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.907</v>
+        <v>0.9352</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.843</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.898</v>
+        <v>0.8981</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8704</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.88</v>
+        <v>0.8796</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.889</v>
+        <v>0.8889</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9074</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8426</v>
       </c>
     </row>
     <row r="8">
@@ -1558,19 +1626,28 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.877</v>
+        <v>0.908</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.828</v>
+        <v>0.9202</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.902</v>
+        <v>0.9018</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8895999999999999</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.902</v>
+        <v>0.9018</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.902</v>
+        <v>0.9018</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8773</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8282</v>
       </c>
     </row>
     <row r="9">
@@ -1580,19 +1657,28 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
+        <v>0.8932</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0.9223</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.9029</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9126</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9126</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.9029</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.9320000000000001</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="I9" t="n">
         <v>0.835</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.903</v>
       </c>
     </row>
     <row r="10">
@@ -1602,19 +1688,28 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.949</v>
+        <v>0.9701</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9658</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9402</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9359</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.953</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.97</v>
+        <v>0.9701</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9487</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9402</v>
       </c>
     </row>
     <row r="11">
@@ -1624,16 +1719,28 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.949</v>
+        <v>0.9745</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.911</v>
+        <v>0.9745</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.968</v>
+        <v>0.9681</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.963</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.958</v>
+        <v>0.9579</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9489</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9106</v>
       </c>
     </row>
     <row r="12">
@@ -1643,19 +1750,28 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.844</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.806</v>
+        <v>0.8728</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.855</v>
+        <v>0.8555</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8121</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.835</v>
+        <v>0.8353</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.855</v>
+        <v>0.8555</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8439</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8064</v>
       </c>
     </row>
     <row r="13">
@@ -1665,16 +1781,28 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.842</v>
+        <v>0.8514</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.708</v>
+        <v>0.8838</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.849</v>
+        <v>0.8492</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7609</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8715000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.869</v>
+        <v>0.8693</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8425</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7084</v>
       </c>
     </row>
     <row r="14">
@@ -1684,17 +1812,29 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.881</v>
+        <v>0.91</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.797</v>
+        <v>0.9164</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.881</v>
       </c>
+      <c r="E14" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8778</v>
+      </c>
       <c r="G14" s="2" t="n">
         <v>0.91</v>
       </c>
+      <c r="H14" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7974</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1703,16 +1843,28 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.745</v>
+        <v>0.9752</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.777</v>
+        <v>0.961</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9362</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9113</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9752</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.979</v>
+        <v>0.9787</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7766</v>
       </c>
     </row>
     <row r="16">
@@ -1722,20 +1874,29 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.8812</v>
+        <v>0.9135</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8011</v>
+        <v>0.9176</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>0.9018</v>
       </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
+      <c r="E16" s="3" t="n">
+        <v>0.8802</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.9071</v>
+      </c>
       <c r="G16" s="4" t="n">
         <v>0.9174</v>
       </c>
-      <c r="H16" s="3" t="n"/>
+      <c r="H16" s="3" t="n">
+        <v>0.8811</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8011</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2547,7 +2708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2792,17 +2953,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>every column</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>mmlu &lt;model&gt;_overall_results.csv</t>
+          <t>Tasks_benchmarks/mmlu/MMLU_*/&lt;vendor&gt;_&lt;Subject&gt;.csv, and MMLU_*/results/&lt;Subject&gt;/&lt;slug&gt;_overall.csv for the two newest slots</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Matches the previous workbook.</t>
+          <t>Refreshed 2026-09-07 from the per-subject files. Every column that has rows has all 13 subjects and 3,943 items. The &lt;vendor&gt;_overall_results.csv roll-ups are NOT the source: Gemma's covers 8 subjects and Qwen's is an empty file, while both have all 13 on disk — the same trap bbh's slot-level roll-up carries.</t>
         </is>
       </c>
     </row>
@@ -2814,17 +2975,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Gemini = gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>mmlu/gemma/gemma_overall_results.csv</t>
+          <t>13 of 13 subjects — two routes</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>8 of 13 subjects; the other five were never written.</t>
+          <t>MMLU_Gemini_Flash3.5lite_Google, 3,943 rows, macro 0.9135, 0 empty, 1 no_marker. TWO ROUTES IN ONE COLUMN: 1,755 rows were answered by OpenRouter on 2026-08-30 before its balance ran out (HTTP 402, limit_source openrouter_credits) and 2,188 by Google AI Studio on 2026-09-07; every row's config column names which. MMLU_Gemini_Flash3.5lite_OpenRouter/ is kept untouched as the record of that first run, 2,188 of whose rows are empty.</t>
         </is>
       </c>
     </row>
@@ -2836,61 +2997,61 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>OpenAI = gpt-5.6-luna</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>13 of 13 subjects</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>qwen_overall_results.csv exists but is empty.</t>
+          <t>MMLU_GPT_5.6_Luna, 3,943 rows, macro 0.9176, 0 empty, 0 no_marker. One route, reasoning_effort=low, the settled config. Run 2026-08-30 as a 5-shard array, merged 2026-09-07.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>MMLU</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Llama</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>blank — never run</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>MMLU_Llama has a runner, an outlog and an empty overall CSV, and no subject files at all — it never produced rows. Llama was never among the six.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>MMLU · DocVQA</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>still per-runner</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Only bbh has been moved onto one shared lenient matcher. Until MMLU and DocVQA follow, their columns are not guaranteed to be scored the same way as each other.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>DocVQA</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Qwen · Gemma</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>two scorers on MMLU</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Two scorers on this sheet. Gemini and OpenAI are scored by mmlu_eval_core.score_response (mmlu_lenient_v1), the one lenient matcher; the other columns carry the score their own runner wrote with ==. A uniform rescore of the seven older slots has not been run, so a small cross-model difference here may be the scorer rather than the model. DocVQA is still per-runner throughout.</t>
         </is>
       </c>
     </row>
@@ -2902,39 +3063,39 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>Qwen · Gemma</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>No DocVQA run exists.</t>
+          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Emo</t>
+          <t>DocVQA</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>XAI · Deepseek</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
+          <t>No DocVQA run exists.</t>
         </is>
       </c>
     </row>
@@ -2946,17 +3107,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
+          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
+          <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
         </is>
       </c>
     </row>
@@ -2968,37 +3129,59 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>XAI · Qwen · Gemma · Deepseek</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>EmoBench/emobench_results.csv</t>
+          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Unchanged.</t>
+          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
+          <t>Emo</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>XAI · Qwen · Gemma · Deepseek</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>EmoBench/emobench_results.csv</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
           <t>Awareness</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>every column</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>No model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
         </is>
